--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/166.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/166.xlsx
@@ -426,13 +426,13 @@
         <v>-13.51300470235037</v>
       </c>
       <c r="E2">
-        <v>-9.657865007444149</v>
+        <v>-7.948569850878935</v>
       </c>
       <c r="F2">
-        <v>-1.173815809464672</v>
+        <v>-1.05464853163274</v>
       </c>
       <c r="G2">
-        <v>-10.08219475851687</v>
+        <v>-12.60684989222047</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.4130061233616</v>
       </c>
       <c r="E3">
-        <v>-9.558908793428538</v>
+        <v>-9.183181305012129</v>
       </c>
       <c r="F3">
-        <v>-1.093470798332342</v>
+        <v>-1.243799601122785</v>
       </c>
       <c r="G3">
-        <v>-10.30460051839065</v>
+        <v>-13.20604870319194</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.17243033782388</v>
       </c>
       <c r="E4">
-        <v>-11.30007082158573</v>
+        <v>-9.751350824858497</v>
       </c>
       <c r="F4">
-        <v>-0.4986185096472114</v>
+        <v>-0.948574428969458</v>
       </c>
       <c r="G4">
-        <v>-10.73238921297527</v>
+        <v>-12.92490062326933</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.80194932427805</v>
       </c>
       <c r="E5">
-        <v>-10.99930769189229</v>
+        <v>-10.71382816197475</v>
       </c>
       <c r="F5">
-        <v>-0.721401295690916</v>
+        <v>-0.6506984811271727</v>
       </c>
       <c r="G5">
-        <v>-10.28626340664862</v>
+        <v>-12.16499137909394</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.32448319553508</v>
       </c>
       <c r="E6">
-        <v>-13.7722372379571</v>
+        <v>-10.49786523654895</v>
       </c>
       <c r="F6">
-        <v>-0.859756876041295</v>
+        <v>-0.3872875874457634</v>
       </c>
       <c r="G6">
-        <v>-10.09652942070191</v>
+        <v>-11.80468153423629</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.77195140685683</v>
       </c>
       <c r="E7">
-        <v>-12.66723523839744</v>
+        <v>-12.19341194602688</v>
       </c>
       <c r="F7">
-        <v>-0.8588655527158827</v>
+        <v>-0.2388656864165648</v>
       </c>
       <c r="G7">
-        <v>-9.51421439198073</v>
+        <v>-12.0369957569091</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.16671809240583</v>
       </c>
       <c r="E8">
-        <v>-14.61325637371362</v>
+        <v>-13.31252467059443</v>
       </c>
       <c r="F8">
-        <v>-0.3218258534395325</v>
+        <v>-0.1941901756487819</v>
       </c>
       <c r="G8">
-        <v>-9.636505944201408</v>
+        <v>-11.93877518130447</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.52630391639903</v>
       </c>
       <c r="E9">
-        <v>-14.37409860442054</v>
+        <v>-14.11244790473135</v>
       </c>
       <c r="F9">
-        <v>-0.9735902961666003</v>
+        <v>-0.2272511470619129</v>
       </c>
       <c r="G9">
-        <v>-8.610044815386063</v>
+        <v>-11.4914675102203</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.8742792141772</v>
       </c>
       <c r="E10">
-        <v>-15.85751347748315</v>
+        <v>-15.31336298377347</v>
       </c>
       <c r="F10">
-        <v>-0.4635031870751375</v>
+        <v>-0.352492843058573</v>
       </c>
       <c r="G10">
-        <v>-8.043256245244061</v>
+        <v>-10.73991408298603</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.223427589914362</v>
       </c>
       <c r="E11">
-        <v>-16.71096327439073</v>
+        <v>-17.15712664752245</v>
       </c>
       <c r="F11">
-        <v>-0.3811974303003814</v>
+        <v>0.136732661360787</v>
       </c>
       <c r="G11">
-        <v>-6.859517718949019</v>
+        <v>-9.879999879160343</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.58456545656888</v>
       </c>
       <c r="E12">
-        <v>-16.23035179948267</v>
+        <v>-16.43084545769827</v>
       </c>
       <c r="F12">
-        <v>-0.3062848525956109</v>
+        <v>0.03687711279032064</v>
       </c>
       <c r="G12">
-        <v>-7.471131075692753</v>
+        <v>-8.909337995409413</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.959939978455108</v>
       </c>
       <c r="E13">
-        <v>-17.19139361033849</v>
+        <v>-16.999227815823</v>
       </c>
       <c r="F13">
-        <v>-0.05817638994611703</v>
+        <v>0.1345267189671319</v>
       </c>
       <c r="G13">
-        <v>-6.976429634668381</v>
+        <v>-8.886558131553688</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.367859549590893</v>
       </c>
       <c r="E14">
-        <v>-18.52830329230495</v>
+        <v>-17.99995717288204</v>
       </c>
       <c r="F14">
-        <v>-0.1272042456213998</v>
+        <v>0.07377756711542742</v>
       </c>
       <c r="G14">
-        <v>-7.503372478699715</v>
+        <v>-7.413309087303842</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.812073084551511</v>
       </c>
       <c r="E15">
-        <v>-21.32249855230978</v>
+        <v>-18.82749051304372</v>
       </c>
       <c r="F15">
-        <v>0.3467196561334477</v>
+        <v>-0.3991912270239923</v>
       </c>
       <c r="G15">
-        <v>-5.44637493951018</v>
+        <v>-6.043501348974064</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.293838848836915</v>
       </c>
       <c r="E16">
-        <v>-20.465978450025</v>
+        <v>-19.45623290121669</v>
       </c>
       <c r="F16">
-        <v>-0.06607735823401871</v>
+        <v>-0.03135385344346904</v>
       </c>
       <c r="G16">
-        <v>-4.450466835476769</v>
+        <v>-5.626680491761046</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.816031127872593</v>
       </c>
       <c r="E17">
-        <v>-20.21021929501979</v>
+        <v>-20.66892201267875</v>
       </c>
       <c r="F17">
-        <v>-0.2949279355032297</v>
+        <v>0.295895174134684</v>
       </c>
       <c r="G17">
-        <v>-4.513430101088168</v>
+        <v>-5.329863599801071</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.379831791708271</v>
       </c>
       <c r="E18">
-        <v>-20.08572701607493</v>
+        <v>-21.56394772945075</v>
       </c>
       <c r="F18">
-        <v>-0.05063161964141914</v>
+        <v>-0.03320194111911474</v>
       </c>
       <c r="G18">
-        <v>-3.500568693348148</v>
+        <v>-5.203854304939791</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.979841339572117</v>
       </c>
       <c r="E19">
-        <v>-22.12270708030918</v>
+        <v>-22.36479930075923</v>
       </c>
       <c r="F19">
-        <v>0.1643918489402625</v>
+        <v>-0.198577209414008</v>
       </c>
       <c r="G19">
-        <v>-2.80153045000334</v>
+        <v>-4.409369723152256</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.607839879215322</v>
       </c>
       <c r="E20">
-        <v>-24.16072869356519</v>
+        <v>-22.67647152433715</v>
       </c>
       <c r="F20">
-        <v>0.3027350037795996</v>
+        <v>0.3417403396752199</v>
       </c>
       <c r="G20">
-        <v>-2.781190458210058</v>
+        <v>-3.292898171669666</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.267450697685363</v>
       </c>
       <c r="E21">
-        <v>-24.15342426499082</v>
+        <v>-23.64068779547234</v>
       </c>
       <c r="F21">
-        <v>0.3996001460259598</v>
+        <v>0.1221641638477521</v>
       </c>
       <c r="G21">
-        <v>-2.830077284188476</v>
+        <v>-3.082036284091327</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.956572250706949</v>
       </c>
       <c r="E22">
-        <v>-22.63808365017412</v>
+        <v>-22.8482456003961</v>
       </c>
       <c r="F22">
-        <v>1.013266315163473</v>
+        <v>0.3101290112169879</v>
       </c>
       <c r="G22">
-        <v>-0.589519926482972</v>
+        <v>-3.083231391031004</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.677314851111335</v>
       </c>
       <c r="E23">
-        <v>-25.65262992691818</v>
+        <v>-23.98986031230777</v>
       </c>
       <c r="F23">
-        <v>0.7480777450356558</v>
+        <v>0.3477609139587667</v>
       </c>
       <c r="G23">
-        <v>-0.6789874196817758</v>
+        <v>-1.209469236894591</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.434749263818033</v>
       </c>
       <c r="E24">
-        <v>-23.58732425776596</v>
+        <v>-24.52157108791839</v>
       </c>
       <c r="F24">
-        <v>0.8354174905172245</v>
+        <v>0.2105145175607362</v>
       </c>
       <c r="G24">
-        <v>-1.026621185669565</v>
+        <v>-1.703584711358512</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.240480632516335</v>
       </c>
       <c r="E25">
-        <v>-25.56577379545107</v>
+        <v>-24.80326481356552</v>
       </c>
       <c r="F25">
-        <v>0.5877091293232827</v>
+        <v>0.3326067606919526</v>
       </c>
       <c r="G25">
-        <v>-0.9809720732285543</v>
+        <v>-1.45776015233993</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.101163730834496</v>
       </c>
       <c r="E26">
-        <v>-25.09041082191789</v>
+        <v>-24.6054746543325</v>
       </c>
       <c r="F26">
-        <v>0.6367973532457786</v>
+        <v>0.265445216775177</v>
       </c>
       <c r="G26">
-        <v>-1.485042358129064</v>
+        <v>-0.7053029461734425</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.024861320137846</v>
       </c>
       <c r="E27">
-        <v>-24.69069147820884</v>
+        <v>-25.1328652657398</v>
       </c>
       <c r="F27">
-        <v>0.6125170763023223</v>
+        <v>0.198822940037624</v>
       </c>
       <c r="G27">
-        <v>-0.3968991448260172</v>
+        <v>-0.5209353545458908</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.022305689960309</v>
       </c>
       <c r="E28">
-        <v>-25.43988221803783</v>
+        <v>-25.07023194173971</v>
       </c>
       <c r="F28">
-        <v>0.5218945108034592</v>
+        <v>0.2589052561300749</v>
       </c>
       <c r="G28">
-        <v>-0.4417702790652989</v>
+        <v>-0.3483599261292231</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.096100566953908</v>
       </c>
       <c r="E29">
-        <v>-25.04369961252877</v>
+        <v>-25.08025345471869</v>
       </c>
       <c r="F29">
-        <v>0.7946005151116816</v>
+        <v>0.6251960677695715</v>
       </c>
       <c r="G29">
-        <v>-1.044842428317713</v>
+        <v>-0.7725798526225116</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.25011844415646</v>
       </c>
       <c r="E30">
-        <v>-24.63559353495752</v>
+        <v>-23.71948324320581</v>
       </c>
       <c r="F30">
-        <v>0.8796672204399685</v>
+        <v>0.00768793061787446</v>
       </c>
       <c r="G30">
-        <v>-0.1541567037044967</v>
+        <v>-0.8316201217698739</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.481822519351977</v>
       </c>
       <c r="E31">
-        <v>-24.48865813883064</v>
+        <v>-23.35748608798065</v>
       </c>
       <c r="F31">
-        <v>0.4827624346952105</v>
+        <v>0.06025281252991989</v>
       </c>
       <c r="G31">
-        <v>-0.3437350940108613</v>
+        <v>-0.9629163578573692</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.788154034827781</v>
       </c>
       <c r="E32">
-        <v>-24.33847129836625</v>
+        <v>-23.21784153500612</v>
       </c>
       <c r="F32">
-        <v>0.4658736800869342</v>
+        <v>-0.08650407001965173</v>
       </c>
       <c r="G32">
-        <v>0.4786474550361121</v>
+        <v>-0.7284734544028015</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.154113982165435</v>
       </c>
       <c r="E33">
-        <v>-22.69623831338063</v>
+        <v>-22.77115738736353</v>
       </c>
       <c r="F33">
-        <v>0.981720427730062</v>
+        <v>-0.02080707967102573</v>
       </c>
       <c r="G33">
-        <v>-0.957798254453656</v>
+        <v>-1.206026269533749</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.570798614871339</v>
       </c>
       <c r="E34">
-        <v>-22.36439626657255</v>
+        <v>-22.41958025083002</v>
       </c>
       <c r="F34">
-        <v>0.1958093394262394</v>
+        <v>-0.6089255697387992</v>
       </c>
       <c r="G34">
-        <v>-2.172278506626369</v>
+        <v>-1.667870546080854</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.024440325851993</v>
       </c>
       <c r="E35">
-        <v>-21.79354589011364</v>
+        <v>-21.29946220503276</v>
       </c>
       <c r="F35">
-        <v>0.4586544581715365</v>
+        <v>0.09448426708320666</v>
       </c>
       <c r="G35">
-        <v>0.335376975733073</v>
+        <v>-1.324378272562694</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.495842927827427</v>
       </c>
       <c r="E36">
-        <v>-22.14929375120821</v>
+        <v>-20.37513273295713</v>
       </c>
       <c r="F36">
-        <v>0.6973684061058812</v>
+        <v>-0.2175990100844931</v>
       </c>
       <c r="G36">
-        <v>-1.735415606718604</v>
+        <v>-2.311040022904921</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.967989598713427</v>
       </c>
       <c r="E37">
-        <v>-21.45389675411634</v>
+        <v>-20.24809545161995</v>
       </c>
       <c r="F37">
-        <v>0.4491100089564806</v>
+        <v>0.1884161603562538</v>
       </c>
       <c r="G37">
-        <v>-2.076173369621327</v>
+        <v>-2.850804609809853</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.426030951229174</v>
       </c>
       <c r="E38">
-        <v>-22.17618835833976</v>
+        <v>-19.87266231401404</v>
       </c>
       <c r="F38">
-        <v>0.997197644283968</v>
+        <v>-0.1996698260183006</v>
       </c>
       <c r="G38">
-        <v>-2.223429745753648</v>
+        <v>-3.098916755796071</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.857530580269575</v>
       </c>
       <c r="E39">
-        <v>-19.13443500975762</v>
+        <v>-19.38744085256617</v>
       </c>
       <c r="F39">
-        <v>0.6229793565996801</v>
+        <v>-0.03196850205634627</v>
       </c>
       <c r="G39">
-        <v>-2.449318199534739</v>
+        <v>-3.52077295277432</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.245007668620308</v>
       </c>
       <c r="E40">
-        <v>-18.67190120308818</v>
+        <v>-18.42797947913903</v>
       </c>
       <c r="F40">
-        <v>0.7524995702317996</v>
+        <v>-0.1133647114228285</v>
       </c>
       <c r="G40">
-        <v>-3.025432576460869</v>
+        <v>-4.056515226849037</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.58346507326351</v>
       </c>
       <c r="E41">
-        <v>-19.41372864418069</v>
+        <v>-17.6977766308242</v>
       </c>
       <c r="F41">
-        <v>1.195951148707264</v>
+        <v>0.06910391822883261</v>
       </c>
       <c r="G41">
-        <v>-2.798997882665798</v>
+        <v>-4.977843360973748</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.868076403640677</v>
       </c>
       <c r="E42">
-        <v>-17.68255190121042</v>
+        <v>-15.85362351831056</v>
       </c>
       <c r="F42">
-        <v>0.8915079040955846</v>
+        <v>0.3143014978248891</v>
       </c>
       <c r="G42">
-        <v>-3.890726416787875</v>
+        <v>-4.642054726925471</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.09752383735113</v>
       </c>
       <c r="E43">
-        <v>-17.57944307652977</v>
+        <v>-15.74008561799025</v>
       </c>
       <c r="F43">
-        <v>0.991235055718617</v>
+        <v>0.7800543835185223</v>
       </c>
       <c r="G43">
-        <v>-4.491408352160936</v>
+        <v>-5.405171889728411</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.271661465362472</v>
       </c>
       <c r="E44">
-        <v>-16.97822022490141</v>
+        <v>-15.77898973819015</v>
       </c>
       <c r="F44">
-        <v>1.211317364029195</v>
+        <v>0.388109033414325</v>
       </c>
       <c r="G44">
-        <v>-5.526513315379319</v>
+        <v>-6.197799255468415</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.396187189701767</v>
       </c>
       <c r="E45">
-        <v>-14.91815400017606</v>
+        <v>-13.74971713671695</v>
       </c>
       <c r="F45">
-        <v>1.256365640128238</v>
+        <v>0.8469798427255</v>
       </c>
       <c r="G45">
-        <v>-5.875239561395067</v>
+        <v>-5.920855568380684</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.478655069007919</v>
       </c>
       <c r="E46">
-        <v>-13.52435309925123</v>
+        <v>-13.09269442836609</v>
       </c>
       <c r="F46">
-        <v>1.092037428230483</v>
+        <v>0.7015748557772972</v>
       </c>
       <c r="G46">
-        <v>-5.982358883409264</v>
+        <v>-6.578637793215094</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.521056336279754</v>
       </c>
       <c r="E47">
-        <v>-14.01927002354953</v>
+        <v>-12.87381063720534</v>
       </c>
       <c r="F47">
-        <v>1.076450867179408</v>
+        <v>0.3811341798827532</v>
       </c>
       <c r="G47">
-        <v>-6.15535475110942</v>
+        <v>-7.464251762062148</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.530701828573211</v>
       </c>
       <c r="E48">
-        <v>-13.51688564561258</v>
+        <v>-12.66462683736902</v>
       </c>
       <c r="F48">
-        <v>1.258471350066154</v>
+        <v>0.9956585376495665</v>
       </c>
       <c r="G48">
-        <v>-6.366729773246345</v>
+        <v>-8.055856181566526</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.509536547206572</v>
       </c>
       <c r="E49">
-        <v>-12.26409236833859</v>
+        <v>-11.8518880217904</v>
       </c>
       <c r="F49">
-        <v>1.495806894642241</v>
+        <v>1.067269242886778</v>
       </c>
       <c r="G49">
-        <v>-6.377061985874411</v>
+        <v>-7.994051606893873</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.463820151204999</v>
       </c>
       <c r="E50">
-        <v>-12.38326369032445</v>
+        <v>-10.72712376166127</v>
       </c>
       <c r="F50">
-        <v>1.423021564427859</v>
+        <v>0.6826831087890516</v>
       </c>
       <c r="G50">
-        <v>-7.229974385884543</v>
+        <v>-8.1229311447377</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.391317606546377</v>
       </c>
       <c r="E51">
-        <v>-11.21494003871553</v>
+        <v>-10.58771016086113</v>
       </c>
       <c r="F51">
-        <v>0.8127318208241572</v>
+        <v>0.9921462598616965</v>
       </c>
       <c r="G51">
-        <v>-8.660980869053288</v>
+        <v>-8.892626361527173</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.292595239556412</v>
       </c>
       <c r="E52">
-        <v>-11.18716237915248</v>
+        <v>-9.749521321359399</v>
       </c>
       <c r="F52">
-        <v>1.224420479606678</v>
+        <v>0.8251473914573162</v>
       </c>
       <c r="G52">
-        <v>-8.668161442327968</v>
+        <v>-9.364398964146552</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.166933533555621</v>
       </c>
       <c r="E53">
-        <v>-9.611045114678847</v>
+        <v>-9.26742450697682</v>
       </c>
       <c r="F53">
-        <v>1.728135786635807</v>
+        <v>0.9028118056741866</v>
       </c>
       <c r="G53">
-        <v>-7.487077973555422</v>
+        <v>-10.65899110782409</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.013543605161107</v>
       </c>
       <c r="E54">
-        <v>-9.467456260843635</v>
+        <v>-8.431386692628733</v>
       </c>
       <c r="F54">
-        <v>1.522879598100534</v>
+        <v>0.7344527579944096</v>
       </c>
       <c r="G54">
-        <v>-7.932885967510298</v>
+        <v>-10.99670316883068</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.829147038196977</v>
       </c>
       <c r="E55">
-        <v>-9.615057342649642</v>
+        <v>-8.272025163824805</v>
       </c>
       <c r="F55">
-        <v>1.643602549914923</v>
+        <v>0.8449983878980035</v>
       </c>
       <c r="G55">
-        <v>-7.895648951284576</v>
+        <v>-9.477205803397219</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.608663713264932</v>
       </c>
       <c r="E56">
-        <v>-8.982578963420346</v>
+        <v>-8.50092593949052</v>
       </c>
       <c r="F56">
-        <v>1.252848392135951</v>
+        <v>0.6418520511376612</v>
       </c>
       <c r="G56">
-        <v>-8.561426143596325</v>
+        <v>-10.75549019974831</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.354277997500716</v>
       </c>
       <c r="E57">
-        <v>-8.24299764543564</v>
+        <v>-7.513650678708267</v>
       </c>
       <c r="F57">
-        <v>1.696029922838104</v>
+        <v>1.167306203918458</v>
       </c>
       <c r="G57">
-        <v>-8.683485957629255</v>
+        <v>-10.72192788907117</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.063383418290666</v>
       </c>
       <c r="E58">
-        <v>-7.698226750786903</v>
+        <v>-6.448906813076797</v>
       </c>
       <c r="F58">
-        <v>1.146913455196339</v>
+        <v>0.6821960287562056</v>
       </c>
       <c r="G58">
-        <v>-8.890815493117191</v>
+        <v>-10.93186944498959</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.734842319454786</v>
       </c>
       <c r="E59">
-        <v>-8.570161778593791</v>
+        <v>-7.493046121973366</v>
       </c>
       <c r="F59">
-        <v>1.597588397424216</v>
+        <v>0.3239171866365858</v>
       </c>
       <c r="G59">
-        <v>-8.171225383064588</v>
+        <v>-10.69048432753918</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.365181210641023</v>
       </c>
       <c r="E60">
-        <v>-6.294630760583483</v>
+        <v>-6.568635137365593</v>
       </c>
       <c r="F60">
-        <v>0.7580860799962794</v>
+        <v>0.5586798220595768</v>
       </c>
       <c r="G60">
-        <v>-7.920739575926712</v>
+        <v>-10.09001757762617</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.959912613672713</v>
       </c>
       <c r="E61">
-        <v>-8.922006095093748</v>
+        <v>-7.360859965689468</v>
       </c>
       <c r="F61">
-        <v>0.7475277090801969</v>
+        <v>0.4301917542113455</v>
       </c>
       <c r="G61">
-        <v>-9.769649464699816</v>
+        <v>-11.1914791156337</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.51857846331111</v>
       </c>
       <c r="E62">
-        <v>-6.000171266708726</v>
+        <v>-6.021455094544777</v>
       </c>
       <c r="F62">
-        <v>1.053173743160742</v>
+        <v>0.5338039489535077</v>
       </c>
       <c r="G62">
-        <v>-8.143463148172259</v>
+        <v>-11.10481565450666</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.03853048323601</v>
       </c>
       <c r="E63">
-        <v>-7.026291777528775</v>
+        <v>-6.46598821703373</v>
       </c>
       <c r="F63">
-        <v>0.5162549855252001</v>
+        <v>0.4553940040741177</v>
       </c>
       <c r="G63">
-        <v>-8.993670832476807</v>
+        <v>-10.62220432579171</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.522438668431644</v>
       </c>
       <c r="E64">
-        <v>-6.497053548726348</v>
+        <v>-5.244106303336098</v>
       </c>
       <c r="F64">
-        <v>0.9204610015582328</v>
+        <v>-0.04932528424720432</v>
       </c>
       <c r="G64">
-        <v>-9.09867802643695</v>
+        <v>-10.68114527857289</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.975175746532819</v>
       </c>
       <c r="E65">
-        <v>-7.887938112390237</v>
+        <v>-5.463153119561121</v>
       </c>
       <c r="F65">
-        <v>0.3911408581085712</v>
+        <v>0.06383715828183335</v>
       </c>
       <c r="G65">
-        <v>-8.041544693200256</v>
+        <v>-10.18905254743347</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.3973243290812</v>
       </c>
       <c r="E66">
-        <v>-5.337030589973494</v>
+        <v>-6.256967442261689</v>
       </c>
       <c r="F66">
-        <v>0.5236067462250458</v>
+        <v>0.1711165355161889</v>
       </c>
       <c r="G66">
-        <v>-7.796117399646388</v>
+        <v>-9.427531067580453</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.78675934039358</v>
       </c>
       <c r="E67">
-        <v>-6.878785793676928</v>
+        <v>-5.321810388833714</v>
       </c>
       <c r="F67">
-        <v>0.3681155577803562</v>
+        <v>-0.06586778128111044</v>
       </c>
       <c r="G67">
-        <v>-7.306779042395635</v>
+        <v>-10.32034216242988</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.151842770551743</v>
       </c>
       <c r="E68">
-        <v>-5.966171483859137</v>
+        <v>-5.862333574863255</v>
       </c>
       <c r="F68">
-        <v>-0.17793595047105</v>
+        <v>-0.08830991095775464</v>
       </c>
       <c r="G68">
-        <v>-7.660414827446123</v>
+        <v>-9.013686390807241</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.500345137701648</v>
       </c>
       <c r="E69">
-        <v>-6.176790809955885</v>
+        <v>-6.032744580245899</v>
       </c>
       <c r="F69">
-        <v>0.3839605694611051</v>
+        <v>-0.09878544513355719</v>
       </c>
       <c r="G69">
-        <v>-6.804781159002709</v>
+        <v>-9.528572227984549</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.8316443084873105</v>
       </c>
       <c r="E70">
-        <v>-6.362508057484455</v>
+        <v>-5.336324148028297</v>
       </c>
       <c r="F70">
-        <v>0.02130794745470393</v>
+        <v>-0.4834411620931188</v>
       </c>
       <c r="G70">
-        <v>-8.175780693726624</v>
+        <v>-8.989903431653117</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.1494119420238657</v>
       </c>
       <c r="E71">
-        <v>-6.949701696637047</v>
+        <v>-4.332098809035334</v>
       </c>
       <c r="F71">
-        <v>0.5206826092931635</v>
+        <v>-0.7184887559026729</v>
       </c>
       <c r="G71">
-        <v>-6.631192703651024</v>
+        <v>-8.353993981196671</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.5356122638405422</v>
       </c>
       <c r="E72">
-        <v>-8.311386659899476</v>
+        <v>-6.505041776875879</v>
       </c>
       <c r="F72">
-        <v>0.1994988878383084</v>
+        <v>-0.6278090330530167</v>
       </c>
       <c r="G72">
-        <v>-6.155953959852027</v>
+        <v>-7.682350502189333</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.21844923158457</v>
       </c>
       <c r="E73">
-        <v>-8.137248720408522</v>
+        <v>-6.391897853794235</v>
       </c>
       <c r="F73">
-        <v>0.04990401856674567</v>
+        <v>-0.6645098508340488</v>
       </c>
       <c r="G73">
-        <v>-6.78328909736176</v>
+        <v>-7.734832580623399</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.89818434127948</v>
       </c>
       <c r="E74">
-        <v>-6.425005527264313</v>
+        <v>-6.81869747206915</v>
       </c>
       <c r="F74">
-        <v>-0.2250352642594242</v>
+        <v>-0.5681036241288395</v>
       </c>
       <c r="G74">
-        <v>-4.368679807929074</v>
+        <v>-6.954685971566447</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>2.56795316042109</v>
       </c>
       <c r="E75">
-        <v>-7.08024401685616</v>
+        <v>-6.897021958505817</v>
       </c>
       <c r="F75">
-        <v>-0.03284988497292494</v>
+        <v>-0.3760126787262593</v>
       </c>
       <c r="G75">
-        <v>-5.087230406682346</v>
+        <v>-6.403910510197901</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.216246485462374</v>
       </c>
       <c r="E76">
-        <v>-7.900169520684955</v>
+        <v>-7.879786859176431</v>
       </c>
       <c r="F76">
-        <v>-0.1349155177740604</v>
+        <v>-0.6352220929406694</v>
       </c>
       <c r="G76">
-        <v>-4.743076024056331</v>
+        <v>-6.153547193244978</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>3.842586367696649</v>
       </c>
       <c r="E77">
-        <v>-7.202562628277344</v>
+        <v>-7.371764531099939</v>
       </c>
       <c r="F77">
-        <v>-0.2830756547039744</v>
+        <v>-1.013942557459173</v>
       </c>
       <c r="G77">
-        <v>-3.835883919384309</v>
+        <v>-5.51342341831704</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>4.443758303662312</v>
       </c>
       <c r="E78">
-        <v>-9.184408521468207</v>
+        <v>-9.359375171702567</v>
       </c>
       <c r="F78">
-        <v>-0.1115000563991268</v>
+        <v>-1.258367270268417</v>
       </c>
       <c r="G78">
-        <v>-3.020969961073931</v>
+        <v>-5.796203597190506</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>5.011149003732491</v>
       </c>
       <c r="E79">
-        <v>-9.62862917925063</v>
+        <v>-9.751341767910482</v>
       </c>
       <c r="F79">
-        <v>-0.1764299785327605</v>
+        <v>-1.517408525900059</v>
       </c>
       <c r="G79">
-        <v>-2.417047001617924</v>
+        <v>-5.117031937626865</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>5.537395602934023</v>
       </c>
       <c r="E80">
-        <v>-10.18708965082455</v>
+        <v>-9.374536502680247</v>
       </c>
       <c r="F80">
-        <v>-0.5447047301019619</v>
+        <v>-0.771703906225916</v>
       </c>
       <c r="G80">
-        <v>-1.987046862613068</v>
+        <v>-3.642223626428023</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>6.023950895061577</v>
       </c>
       <c r="E81">
-        <v>-10.57142576832955</v>
+        <v>-10.62499761584029</v>
       </c>
       <c r="F81">
-        <v>-0.4051944055920803</v>
+        <v>-1.251939967590096</v>
       </c>
       <c r="G81">
-        <v>-1.14438060104698</v>
+        <v>-3.083648519768952</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>6.46893942286005</v>
       </c>
       <c r="E82">
-        <v>-12.81097353187491</v>
+        <v>-11.87536815952017</v>
       </c>
       <c r="F82">
-        <v>-0.9200769335783494</v>
+        <v>-0.7496386837175456</v>
       </c>
       <c r="G82">
-        <v>-0.869684774380414</v>
+        <v>-2.774536261676123</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>6.865587810697296</v>
       </c>
       <c r="E83">
-        <v>-14.0214980327613</v>
+        <v>-13.26302392121659</v>
       </c>
       <c r="F83">
-        <v>-1.083985163202885</v>
+        <v>-1.465006003998962</v>
       </c>
       <c r="G83">
-        <v>-0.2938981414626728</v>
+        <v>-1.228432041743536</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>7.215322199003825</v>
       </c>
       <c r="E84">
-        <v>-13.22868450281643</v>
+        <v>-13.92387771857795</v>
       </c>
       <c r="F84">
-        <v>-0.5040782791990629</v>
+        <v>-1.218993310878551</v>
       </c>
       <c r="G84">
-        <v>0.5116767678814208</v>
+        <v>-0.7647338596944389</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>7.519780017861216</v>
       </c>
       <c r="E85">
-        <v>-16.65413545406848</v>
+        <v>-15.05929747804713</v>
       </c>
       <c r="F85">
-        <v>-1.33053463840031</v>
+        <v>-1.448951415365305</v>
       </c>
       <c r="G85">
-        <v>0.7856806905302791</v>
+        <v>-0.4889025159079028</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>7.777459765928967</v>
       </c>
       <c r="E86">
-        <v>-17.44083101562899</v>
+        <v>-16.66002247027845</v>
       </c>
       <c r="F86">
-        <v>-1.219448084582688</v>
+        <v>-1.538251078121897</v>
       </c>
       <c r="G86">
-        <v>1.140140801420045</v>
+        <v>-0.001709392166597846</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>7.983297534544558</v>
       </c>
       <c r="E87">
-        <v>-19.73662695482362</v>
+        <v>-17.36088533549757</v>
       </c>
       <c r="F87">
-        <v>-1.267911719483473</v>
+        <v>-1.504886095871939</v>
       </c>
       <c r="G87">
-        <v>0.7181654248023825</v>
+        <v>0.4030974952844044</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>8.137709127834448</v>
       </c>
       <c r="E88">
-        <v>-17.72681320616138</v>
+        <v>-18.97187184983027</v>
       </c>
       <c r="F88">
-        <v>-1.073020892259431</v>
+        <v>-1.376824637236149</v>
       </c>
       <c r="G88">
-        <v>1.049534480555732</v>
+        <v>1.117079541193482</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>8.236597622428032</v>
       </c>
       <c r="E89">
-        <v>-20.92353093528601</v>
+        <v>-19.30230101274796</v>
       </c>
       <c r="F89">
-        <v>-1.62747701617964</v>
+        <v>-1.486456577894455</v>
       </c>
       <c r="G89">
-        <v>0.980794312978305</v>
+        <v>0.8809846755148181</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>8.275297359252564</v>
       </c>
       <c r="E90">
-        <v>-23.41014771221585</v>
+        <v>-21.3501403576526</v>
       </c>
       <c r="F90">
-        <v>-1.530232481662798</v>
+        <v>-1.876186045196164</v>
       </c>
       <c r="G90">
-        <v>1.630505427787972</v>
+        <v>1.610585875278177</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>8.247681424266551</v>
       </c>
       <c r="E91">
-        <v>-24.01255702403422</v>
+        <v>-23.20787889218925</v>
       </c>
       <c r="F91">
-        <v>-2.051553081103625</v>
+        <v>-1.721144660251195</v>
       </c>
       <c r="G91">
-        <v>2.801544701394369</v>
+        <v>0.7463514095237374</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>8.14742308531287</v>
       </c>
       <c r="E92">
-        <v>-26.44112329265974</v>
+        <v>-25.60953243978718</v>
       </c>
       <c r="F92">
-        <v>-1.990133780023056</v>
+        <v>-1.829787530230558</v>
       </c>
       <c r="G92">
-        <v>1.636414751575571</v>
+        <v>1.793966924335026</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>7.972680659686676</v>
       </c>
       <c r="E93">
-        <v>-26.93654287757288</v>
+        <v>-26.87785385443348</v>
       </c>
       <c r="F93">
-        <v>-1.787348611450334</v>
+        <v>-1.805770674121192</v>
       </c>
       <c r="G93">
-        <v>1.55547191314039</v>
+        <v>0.8977956257632371</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.718596396060662</v>
       </c>
       <c r="E94">
-        <v>-28.46934075968915</v>
+        <v>-28.63187222029844</v>
       </c>
       <c r="F94">
-        <v>-1.584464867156679</v>
+        <v>-1.88548198419038</v>
       </c>
       <c r="G94">
-        <v>1.639069809098066</v>
+        <v>1.645853116908033</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.38761038298111</v>
       </c>
       <c r="E95">
-        <v>-31.80323502345411</v>
+        <v>-30.74320982773864</v>
       </c>
       <c r="F95">
-        <v>-1.9611193833726</v>
+        <v>-1.925222081972284</v>
       </c>
       <c r="G95">
-        <v>2.027148509939131</v>
+        <v>0.6576751367088194</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.97292015427753</v>
       </c>
       <c r="E96">
-        <v>-32.64968606378284</v>
+        <v>-31.68268704536993</v>
       </c>
       <c r="F96">
-        <v>-2.720075396389327</v>
+        <v>-2.419368917131675</v>
       </c>
       <c r="G96">
-        <v>1.34675194852596</v>
+        <v>1.244244216447967</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.494271693303967</v>
       </c>
       <c r="E97">
-        <v>-34.8722271431924</v>
+        <v>-35.3276580383808</v>
       </c>
       <c r="F97">
-        <v>-2.601579924521066</v>
+        <v>-2.031197608914633</v>
       </c>
       <c r="G97">
-        <v>0.3745738349180438</v>
+        <v>0.3007850853932283</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.939435434484107</v>
       </c>
       <c r="E98">
-        <v>-37.61296829601068</v>
+        <v>-36.78609158458011</v>
       </c>
       <c r="F98">
-        <v>-2.704561731669698</v>
+        <v>-2.469939918705182</v>
       </c>
       <c r="G98">
-        <v>1.697937929877387</v>
+        <v>0.7491024728668717</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.343381795904533</v>
       </c>
       <c r="E99">
-        <v>-37.17371537421467</v>
+        <v>-38.95495439733974</v>
       </c>
       <c r="F99">
-        <v>-3.382296320841933</v>
+        <v>-2.579636472020907</v>
       </c>
       <c r="G99">
-        <v>0.2751978789202013</v>
+        <v>0.04197325622408547</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.675144039054067</v>
       </c>
       <c r="E100">
-        <v>-40.73280838614409</v>
+        <v>-42.74978618068645</v>
       </c>
       <c r="F100">
-        <v>-3.329066259905439</v>
+        <v>-2.790236458671639</v>
       </c>
       <c r="G100">
-        <v>-0.08740286345063253</v>
+        <v>-1.248060266245875</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.013047736704618</v>
       </c>
       <c r="E101">
-        <v>-43.15401814874414</v>
+        <v>-43.00753560001803</v>
       </c>
       <c r="F101">
-        <v>-3.227467826319483</v>
+        <v>-2.848071414000295</v>
       </c>
       <c r="G101">
-        <v>0.2655708124920007</v>
+        <v>-0.9243352601427027</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.250117671488098</v>
       </c>
       <c r="E102">
-        <v>-44.87382389348116</v>
+        <v>-45.57842048551961</v>
       </c>
       <c r="F102">
-        <v>-3.488226287577128</v>
+        <v>-3.033819550199639</v>
       </c>
       <c r="G102">
-        <v>-1.348078468078336</v>
+        <v>-1.417854836409555</v>
       </c>
     </row>
   </sheetData>
